--- a/deliverables/青岛抚顺路和哈尔滨路路口交通事故_肇事方沟通流程表_20260817.xlsx
+++ b/deliverables/青岛抚顺路和哈尔滨路路口交通事故_肇事方沟通流程表_20260817.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>我是伤者胡某的儿子胡继刚。8 月 14 日抚顺路和哈尔滨路路口，你骑美团二轮、我父亲骑三轮，监控交警已经调取。父亲 64 岁，齐鲁医院 CT 证实右腿两处骨折、脚踝半脱位，15 日已经做了内外固定，检查号我可以发给你。今天不谈总赔偿、不谈伤残。就三件事：第一，把你们站点负责人和保险公司拉进一个群；第二，确认市北区人民医院后续费用你们保险认不认；第三，已发生的住院手术费怎么先处理，我们有发票。交警说任何一方都不是全责，我们接受看视频、看认定书。但人还在医院，不能等认定书才开始过问。</t>
+          <t>我是伤者胡某的儿子胡继刚。8 月 14 日抚顺路和哈尔滨路路口，你骑美团二轮、我父亲骑三轮，监控交警已经调取。父亲 64 岁，齐鲁医院病历证实右踝开放性骨折脱位，14 日晚上已经做了内外固定和清创，检查号我可以发给你。今天不谈总赔偿、不谈伤残。就三件事：第一，把你们站点负责人和保险公司拉进一个群；第二，确认市北区人民医院后续费用你们保险认不认；第三，已发生的住院手术费怎么先处理，我们有发票。交警说任何一方都不是全责，我们接受看视频、看认定书。但人还在医院，不能等认定书才开始过问。</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>这不是入职体检，也不是伤残鉴定书。是山东大学齐鲁医院（青岛）2026-08-14、08-15 的三份已审核 CT。 伤者：胡某，男，64 岁。只有他受伤。家属、骑手都没有本次伤残材料。 本次事故造成：右胫骨远端骨折（移位）、右腓骨近端骨折（移位）、右踝关节半脱位、距骨内缘撕脱骨折、外踝撕脱骨折，小腿和踝软组织肿胀。 8 月 15 日已在手足与显微重建外科做右踝内外固定，复查固定在位、位线可，软组织仍肿。到 8 月 17 日术后只有两天，不是康复期。 右足 CT 没有新发骨折。跟骨骨刺、退变、第一跖骨头囊变是陈旧改变，不要向肇事方索赔，也不要说成跟骨粉碎骨折。 现在不能报伤残等级。CT 只能证明伤了什么、做了什么手术，不能定残。</t>
+          <t>这不是入职体检，也不是伤残鉴定书。依据是山东大学齐鲁医院（青岛）三份已审核 CT，以及 8 月 19 日归档的出院记录、急诊病历。 伤者：胡志远，男，64 岁。门诊号 0002750430，住院号 0001519455。只有他受伤。 本次事故造成：右开放性踝关节骨折脱位、韧带断裂、皮肤坏死；右胫骨远端、腓骨近端骨折（移位）；距骨内缘及外踝撕脱骨折。 手术是 8 月 14 日 19:01，切开复位内外固定、韧带缝合、清创、VSD。8 月 15 日术后 CT 固定在位、仍肿。8 月 17 日出院时仍带外固定架、克氏针和负压吸引，不是康复期。 右足 CT 没有新发骨折。跟骨骨刺、退变、第一跖骨头囊变是陈旧改变，不要向肇事方索赔，也不要说成跟骨粉碎骨折。 现在不能报伤残等级。CT 只能证明伤了什么、做了什么手术，不能定残。</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>对肇事方只说报告上有的话：两处骨折、脚踝半脱位、已手术、还在肿、还要住院。</t>
+          <t>对肇事方只说报告和出院记录上有的话：开放性踝关节骨折脱位、已手术、还在肿、还要换药和二期治疗。</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>齐鲁入院记录、手术记录、术后医嘱（向医院要，不要口述钢钉根数）</t>
+          <t>齐鲁入院记录、出院记录、手术记录、术后医嘱（出院记录已有；完整手术记录向病案室要，不要口述钢钉根数）</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>8 月 15 日已经手术，内外固定都在。现在还肿，不是出院养伤阶段。后续还要住院、换药、复查，费用还在发生。</t>
+          <t>8 月 14 日晚上已经手术，内外固定和外固定架都在，还做了清创负压引流。现在还肿、还要换药，不是出院养伤阶段。</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">

--- a/deliverables/青岛抚顺路和哈尔滨路路口交通事故_肇事方沟通流程表_20260817.xlsx
+++ b/deliverables/青岛抚顺路和哈尔滨路路口交通事故_肇事方沟通流程表_20260817.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>现在不要请诉讼律师去跟肇事者当面谈，也不要先发律师函。对内请岳父把关即可。 岳父是执业律师，本周只做三件事：看出院入院手续、看对保险怎么问、看第一次跟骑手的开场稿。不进群、不到场、不署名函。</t>
+          <t>家属已请岳父（执业三十余年）把关。现在仍不到场见骑手或刘孝春，也不先发律师函。 岳父本周场外做五件事：看 3 万收据和欠薪表述；看护工合同（一对一、300 元/天、发票）；指导对保险怎么问；看监控后书面意见简易或一般；认定书签字前给意见。不进群、不到场、不署名函。对外不要对骑手或刘孝春说「我岳父是律师」。</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>责任认定书还没出，谈不了比例。；保险还没进场，律师函容易把骑手吓跑，交警简易调解的空间变小。；己方三轮无正规号牌，一般程序可能带来无牌上路、甚至无证驾驶的治安处罚，不宜用「去走一般程序」威胁对方。；伤残未评，律师现在无法代表你报一个合法残级。</t>
+          <t>责任认定书还没出，谈不了比例。；保险还没进场，律师函容易把骑手吓跑，交警简易调解的空间变小。；己方三轮无正规号牌，一般程序可能带来无牌上路的治安处罚，不宜用「去走一般程序」威胁对方。；伤残未评，现在无法代表报一个合法残级。</t>
         </is>
       </c>
     </row>
